--- a/docs/d/30/inyear.xlsx
+++ b/docs/d/30/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,11 @@
       <c r="AB17" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC17" s="4" t="inlineStr"/>
+      <c r="AC17" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -11702,7 +11706,11 @@
       <c r="AB109" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC109" s="4" t="inlineStr"/>
+      <c r="AC109" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">

--- a/docs/d/30/inyear.xlsx
+++ b/docs/d/30/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 80 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 75 clubs short</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1203,8 +1203,8 @@
       <c r="S5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T5" s="9" t="n">
-        <v>0</v>
+      <c r="T5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U5" s="9" t="n">
         <v>0</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2970,8 +2970,8 @@
       <c r="Y22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="9" t="n">
-        <v>0</v>
+      <c r="Z22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA22" s="10" t="n">
         <v>1</v>
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="P28" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>0</v>
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9497,8 +9497,8 @@
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
@@ -9825,7 +9825,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9895,8 +9895,8 @@
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="9" t="n">
-        <v>0</v>
+      <c r="Z91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
@@ -11522,7 +11522,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11592,8 +11592,8 @@
       <c r="Y108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z108" s="9" t="n">
-        <v>0</v>
+      <c r="Z108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA108" s="10" t="n">
         <v>1</v>
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11802,8 +11802,8 @@
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="9" t="n">
-        <v>0</v>
+      <c r="Z110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
@@ -13725,7 +13725,7 @@
         <v>0</v>
       </c>
       <c r="S129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T129" s="9" t="n">
         <v>0</v>
@@ -14170,7 +14170,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14222,8 +14222,8 @@
       <c r="S134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T134" s="9" t="n">
-        <v>0</v>
+      <c r="T134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U134" s="9" t="n">
         <v>0</v>
@@ -15624,7 +15624,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -15723,7 +15723,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16152,7 +16152,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16284,7 +16284,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -16449,7 +16449,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>

--- a/docs/d/30/inyear.xlsx
+++ b/docs/d/30/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 75 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 47 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -918,8 +918,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="P8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="9" t="n">
         <v>1</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2045,8 +2045,8 @@
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
+      <c r="Z13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA13" s="10" t="n">
         <v>1</v>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2432,8 +2432,8 @@
       <c r="R17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S17" s="9" t="n">
-        <v>1</v>
+      <c r="S17" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T17" s="9" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3461,8 +3461,8 @@
       <c r="S27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T27" s="9" t="n">
-        <v>0</v>
+      <c r="T27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U27" s="9" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>0</v>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3776,8 +3776,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -3948,7 +3948,7 @@
         <v>1</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" s="9" t="n">
         <v>0</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4271,8 +4271,8 @@
       <c r="Y35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" s="9" t="n">
-        <v>0</v>
+      <c r="Z35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA35" s="10" t="n">
         <v>1</v>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4667,8 +4667,8 @@
       <c r="Y39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" s="9" t="n">
-        <v>0</v>
+      <c r="Z39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA39" s="10" t="n">
         <v>1</v>
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4766,8 +4766,8 @@
       <c r="Y40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z40" s="9" t="n">
-        <v>0</v>
+      <c r="Z40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA40" s="10" t="n">
         <v>1</v>
@@ -5034,7 +5034,7 @@
         </is>
       </c>
       <c r="P43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q43" s="9" t="n">
         <v>1</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5459,8 +5459,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5855,8 +5855,8 @@
       <c r="Y51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="n">
-        <v>0</v>
+      <c r="Z51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="10" t="n">
         <v>1</v>
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6748,8 +6748,8 @@
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="9" t="n">
-        <v>0</v>
+      <c r="Z60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA60" s="10" t="n">
         <v>1</v>
@@ -7239,8 +7239,8 @@
       <c r="W65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X65" s="9" t="n">
-        <v>3</v>
+      <c r="X65" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y65" s="9" t="n">
         <v>0</v>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7344,8 +7344,8 @@
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7449,8 +7449,8 @@
       <c r="Y67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z67" s="9" t="n">
-        <v>0</v>
+      <c r="Z67" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA67" s="10" t="n">
         <v>1</v>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7659,8 +7659,8 @@
       <c r="Y69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" s="9" t="n">
-        <v>0</v>
+      <c r="Z69" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA69" s="10" t="n">
         <v>1</v>
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8685,8 +8685,8 @@
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
@@ -8716,7 +8716,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8730,13 +8730,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -8786,8 +8786,8 @@
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="9" t="n">
-        <v>0</v>
+      <c r="Z80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA80" s="10" t="n">
         <v>1</v>
@@ -9019,7 +9019,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -9089,8 +9089,8 @@
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="9" t="n">
-        <v>0</v>
+      <c r="Z83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="10" t="n">
         <v>1</v>
@@ -9326,7 +9326,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9396,8 +9396,8 @@
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="9" t="n">
-        <v>0</v>
+      <c r="Z86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA86" s="10" t="n">
         <v>1</v>
@@ -9726,7 +9726,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9796,8 +9796,8 @@
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="9" t="n">
-        <v>0</v>
+      <c r="Z90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA90" s="10" t="n">
         <v>1</v>
@@ -9924,7 +9924,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -9938,17 +9938,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -9982,11 +9982,11 @@
       <c r="U92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V92" s="9" t="n">
-        <v>0</v>
+      <c r="V92" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X92" s="9" t="n">
         <v>0</v>
@@ -9994,8 +9994,8 @@
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="9" t="n">
         <v>0</v>
@@ -10178,7 +10178,7 @@
         <v>1</v>
       </c>
       <c r="U94" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V94" s="9" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="X97" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
@@ -10920,7 +10920,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10990,8 +10990,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -11120,7 +11120,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11190,8 +11190,8 @@
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="9" t="n">
-        <v>0</v>
+      <c r="Z104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
@@ -11417,7 +11417,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11487,8 +11487,8 @@
       <c r="Y107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z107" s="9" t="n">
-        <v>0</v>
+      <c r="Z107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA107" s="10" t="n">
         <v>1</v>
@@ -11563,7 +11563,7 @@
         </is>
       </c>
       <c r="P108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q108" s="9" t="n">
         <v>0</v>
@@ -11979,7 +11979,7 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q112" s="9" t="n">
         <v>0</v>
@@ -12140,7 +12140,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12210,8 +12210,8 @@
       <c r="Y114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" s="9" t="n">
-        <v>0</v>
+      <c r="Z114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA114" s="10" t="n">
         <v>1</v>
@@ -13024,8 +13024,8 @@
       <c r="W122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X122" s="9" t="n">
-        <v>3</v>
+      <c r="X122" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
@@ -13321,7 +13321,7 @@
         <v>0</v>
       </c>
       <c r="S125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T125" s="9" t="n">
         <v>0</v>
@@ -13376,7 +13376,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -13446,8 +13446,8 @@
       <c r="Y126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z126" s="9" t="n">
-        <v>0</v>
+      <c r="Z126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA126" s="10" t="n">
         <v>1</v>
@@ -13972,7 +13972,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14042,8 +14042,8 @@
       <c r="Y132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z132" s="9" t="n">
-        <v>0</v>
+      <c r="Z132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA132" s="10" t="n">
         <v>1</v>
@@ -14566,7 +14566,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14636,8 +14636,8 @@
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
@@ -14679,13 +14679,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
@@ -14962,7 +14962,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -14976,13 +14976,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -15020,11 +15020,11 @@
       <c r="U142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V142" s="9" t="n">
-        <v>3</v>
+      <c r="V142" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X142" s="10" t="n">
         <v>7</v>
@@ -15131,8 +15131,8 @@
       <c r="Y143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z143" s="9" t="n">
-        <v>0</v>
+      <c r="Z143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA143" s="9" t="n">
         <v>0</v>
@@ -15259,7 +15259,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -15329,8 +15329,8 @@
       <c r="Y145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z145" s="9" t="n">
-        <v>0</v>
+      <c r="Z145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA145" s="10" t="n">
         <v>1</v>
@@ -15358,7 +15358,7 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -15428,8 +15428,8 @@
       <c r="Y146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z146" s="9" t="n">
-        <v>0</v>
+      <c r="Z146" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA146" s="10" t="n">
         <v>1</v>
@@ -15624,7 +15624,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -15690,7 +15690,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -15756,7 +15756,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -15789,7 +15789,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -15822,7 +15822,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -15888,7 +15888,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -15921,7 +15921,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -16020,7 +16020,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16086,7 +16086,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16152,7 +16152,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16185,7 +16185,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16200,7 +16200,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -16251,7 +16251,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -16284,7 +16284,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -16317,7 +16317,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -16383,7 +16383,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -16416,7 +16416,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -16482,7 +16482,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -16515,7 +16515,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>

--- a/docs/d/30/inyear.xlsx
+++ b/docs/d/30/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 47 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 47 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -906,8 +906,8 @@
       <c r="U2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V2" s="9" t="n">
-        <v>2</v>
+      <c r="V2" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1209,8 +1209,8 @@
       <c r="U5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="9" t="n">
-        <v>2</v>
+      <c r="V5" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1270,13 +1270,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="P7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="9" t="n">
         <v>0</v>
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1505,8 +1505,8 @@
       <c r="P8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" s="9" t="n">
-        <v>1</v>
+      <c r="Q8" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R8" s="9" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1577,13 +1577,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1678,13 +1678,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1722,8 +1722,8 @@
       <c r="U10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="9" t="n">
-        <v>3</v>
+      <c r="V10" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1779,13 +1779,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1884,17 +1884,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2195,13 +2195,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2296,13 +2296,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2397,13 +2397,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1</v>
+        <v>-12</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2502,13 +2502,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -2546,8 +2546,8 @@
       <c r="U18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="9" t="n">
-        <v>3</v>
+      <c r="V18" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -2607,13 +2607,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2914,17 +2914,17 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M22" s="8" t="n">
@@ -2959,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3019,17 +3019,17 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M23" s="8" t="n">
@@ -3063,11 +3063,11 @@
       <c r="U23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="9" t="n">
-        <v>2</v>
+      <c r="V23" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" s="10" t="n">
         <v>6</v>
@@ -3223,13 +3223,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3324,13 +3324,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3423,13 +3423,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3522,17 +3522,17 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M28" s="8" t="n">
@@ -3567,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3607,7 +3607,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3621,13 +3621,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3665,8 +3665,8 @@
       <c r="U29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="9" t="n">
-        <v>3</v>
+      <c r="V29" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3720,17 +3720,17 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M30" s="8" t="n">
@@ -3767,8 +3767,8 @@
       <c r="V30" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W30" s="9" t="n">
-        <v>2</v>
+      <c r="W30" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X30" s="9" t="n">
         <v>3</v>
@@ -3918,13 +3918,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4017,17 +4017,17 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M33" s="8" t="n">
@@ -4064,8 +4064,8 @@
       <c r="V33" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W33" s="9" t="n">
-        <v>2</v>
+      <c r="W33" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X33" s="9" t="n">
         <v>0</v>
@@ -4116,13 +4116,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>0</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" s="9" t="n">
         <v>0</v>
@@ -4260,7 +4260,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4314,13 +4314,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4512,13 +4512,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4611,13 +4611,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4809,17 +4809,17 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M41" s="8" t="n">
@@ -4853,11 +4853,11 @@
       <c r="U41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V41" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W41" s="9" t="n">
-        <v>0</v>
+      <c r="V41" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W41" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X41" s="10" t="n">
         <v>7</v>
@@ -4908,13 +4908,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5304,17 +5304,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M46" s="8" t="n">
@@ -5348,11 +5348,11 @@
       <c r="U46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="9" t="n">
+      <c r="V46" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W46" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="W46" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X46" s="10" t="n">
         <v>6</v>
@@ -5403,13 +5403,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5502,17 +5502,17 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-40</v>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M48" s="8" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5898,13 +5898,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -6096,17 +6096,17 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-25</v>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M54" s="8" t="n">
@@ -6195,17 +6195,17 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M55" s="8" t="n">
@@ -6240,7 +6240,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6294,13 +6294,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
@@ -6393,13 +6393,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6591,17 +6591,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-24</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M59" s="8" t="n">
@@ -6692,13 +6692,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -6890,13 +6890,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -6991,13 +6991,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7090,13 +7090,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7189,17 +7189,17 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M65" s="8" t="n">
@@ -7234,7 +7234,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7288,13 +7288,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7393,17 +7393,17 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M67" s="8" t="n">
@@ -7437,8 +7437,8 @@
       <c r="U67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V67" s="9" t="n">
-        <v>3</v>
+      <c r="V67" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7498,17 +7498,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M68" s="8" t="n">
@@ -7543,7 +7543,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7603,13 +7603,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7704,13 +7704,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7809,17 +7809,17 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M71" s="8" t="n">
@@ -7910,13 +7910,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -8112,17 +8112,17 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M74" s="8" t="n">
@@ -8157,7 +8157,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8217,13 +8217,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8322,13 +8322,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8423,17 +8423,17 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M77" s="8" t="n">
@@ -8450,7 +8450,7 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q77" s="9" t="n">
         <v>0</v>
@@ -8528,13 +8528,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8629,13 +8629,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8730,13 +8730,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8831,13 +8831,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -9033,13 +9033,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         </is>
       </c>
       <c r="P83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q83" s="9" t="n">
         <v>0</v>
@@ -9077,11 +9077,11 @@
       <c r="U83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W83" s="9" t="n">
-        <v>0</v>
+      <c r="V83" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W83" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X83" s="9" t="n">
         <v>2</v>
@@ -9134,13 +9134,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9340,13 +9340,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>0</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9542,13 +9542,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9641,13 +9641,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9740,13 +9740,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9839,17 +9839,17 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M91" s="8" t="n">
@@ -10037,13 +10037,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10235,13 +10235,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -10433,17 +10433,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M97" s="8" t="n">
@@ -10518,7 +10518,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10532,13 +10532,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10570,11 +10570,11 @@
       <c r="S98" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U98" s="9" t="n">
-        <v>0</v>
+      <c r="T98" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V98" s="9" t="n">
         <v>1</v>
@@ -10631,13 +10631,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10736,13 +10736,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>0</v>
       </c>
       <c r="S100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T100" s="10" t="n">
         <v>1</v>
@@ -10781,7 +10781,7 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10835,13 +10835,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -10879,8 +10879,8 @@
       <c r="U101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V101" s="9" t="n">
-        <v>3</v>
+      <c r="V101" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -10934,13 +10934,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11033,13 +11033,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11134,17 +11134,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M104" s="8" t="n">
@@ -11233,17 +11233,17 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L105" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M105" s="8" t="n">
@@ -11281,7 +11281,7 @@
         <v>4</v>
       </c>
       <c r="W105" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>5</v>
@@ -11332,17 +11332,17 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M106" s="8" t="n">
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -11431,13 +11431,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11536,13 +11536,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11641,13 +11641,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11746,13 +11746,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11851,13 +11851,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -11952,13 +11952,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>4</v>
       </c>
       <c r="W112" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X112" s="10" t="n">
         <v>5</v>
@@ -12053,17 +12053,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-49</v>
+      </c>
+      <c r="L113" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M113" s="8" t="n">
@@ -12154,13 +12154,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12259,17 +12259,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M115" s="8" t="n">
@@ -12364,17 +12364,17 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L116" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L116" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M116" s="8" t="n">
@@ -12409,7 +12409,7 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -12465,17 +12465,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M117" s="8" t="n">
@@ -12566,17 +12566,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12716,7 +12716,7 @@
         <v>0</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
@@ -12772,13 +12772,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>0</v>
       </c>
       <c r="Q120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R120" s="9" t="n">
         <v>0</v>
@@ -12873,13 +12873,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12974,17 +12974,17 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L122" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M122" s="8" t="n">
@@ -13012,8 +13012,8 @@
       <c r="S122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T122" s="9" t="n">
-        <v>0</v>
+      <c r="T122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U122" s="9" t="n">
         <v>0</v>
@@ -13079,13 +13079,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13184,13 +13184,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13285,17 +13285,17 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L125" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M125" s="8" t="n">
@@ -13390,17 +13390,17 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L126" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M126" s="8" t="n">
@@ -13435,7 +13435,7 @@
         <v>0</v>
       </c>
       <c r="V126" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
@@ -13491,13 +13491,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13689,13 +13689,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13788,13 +13788,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
@@ -13887,13 +13887,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -13986,13 +13986,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -14283,13 +14283,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -14382,17 +14382,17 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M136" s="8" t="n">
@@ -14481,13 +14481,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14580,13 +14580,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
@@ -14679,13 +14679,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14778,13 +14778,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -14877,13 +14877,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -14976,13 +14976,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>0</v>
       </c>
       <c r="S142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T142" s="9" t="n">
         <v>0</v>
@@ -15075,13 +15075,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15174,13 +15174,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>0</v>
       </c>
       <c r="V144" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W144" s="9" t="n">
         <v>0</v>
@@ -15273,13 +15273,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -15372,13 +15372,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>0</v>
       </c>
       <c r="Q146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R146" s="9" t="n">
         <v>0</v>
@@ -15416,11 +15416,11 @@
       <c r="U146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V146" s="9" t="n">
-        <v>2</v>
+      <c r="V146" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X146" s="10" t="n">
         <v>7</v>
@@ -15471,13 +15471,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -15657,7 +15657,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15672,7 +15672,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -15690,7 +15690,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -15723,7 +15723,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15738,7 +15738,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -15771,7 +15771,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -15789,7 +15789,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -15804,7 +15804,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -15855,7 +15855,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -15870,7 +15870,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -15888,7 +15888,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -15903,7 +15903,7 @@
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -15936,7 +15936,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -15969,7 +15969,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -16002,7 +16002,7 @@
         <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -16020,7 +16020,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16035,7 +16035,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -16068,7 +16068,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -16101,7 +16101,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -16119,7 +16119,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16167,7 +16167,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -16218,7 +16218,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16233,7 +16233,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -16266,7 +16266,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -16332,7 +16332,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -16365,7 +16365,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -16383,7 +16383,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -16398,7 +16398,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -16464,7 +16464,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -16515,7 +16515,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>

--- a/docs/d/30/inyear.xlsx
+++ b/docs/d/30/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/30/inyear.xlsx
+++ b/docs/d/30/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/30/inyear.xlsx
+++ b/docs/d/30/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/30/inyear.xlsx
+++ b/docs/d/30/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/30/inyear.xlsx
+++ b/docs/d/30/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 47 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 47 clubs short</t>
         </is>
       </c>
     </row>
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -2195,13 +2195,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="P17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="9" t="n">
         <v>0</v>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2607,13 +2607,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2651,8 +2651,8 @@
       <c r="U19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V19" s="9" t="n">
-        <v>2</v>
+      <c r="V19" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -3019,13 +3019,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>4</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X23" s="10" t="n">
         <v>6</v>
@@ -3423,13 +3423,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3720,17 +3720,17 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M30" s="8" t="n">
@@ -3768,7 +3768,7 @@
         <v>4</v>
       </c>
       <c r="W30" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X30" s="9" t="n">
         <v>3</v>
@@ -3918,13 +3918,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>4</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X32" s="10" t="n">
         <v>4</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4215,13 +4215,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4259,8 +4259,8 @@
       <c r="U35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="9" t="n">
-        <v>3</v>
+      <c r="V35" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -5007,13 +5007,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -5304,17 +5304,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L46" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M46" s="8" t="n">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="P46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" s="9" t="n">
         <v>0</v>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>0</v>
       </c>
       <c r="S56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" s="9" t="n">
         <v>0</v>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -7090,13 +7090,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-15</v>
+        <v>-3</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7189,13 +7189,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q65" s="9" t="n">
         <v>0</v>
@@ -7393,13 +7393,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7809,17 +7809,17 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L71" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M71" s="8" t="n">
@@ -8217,13 +8217,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8831,13 +8831,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9033,13 +9033,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9279,8 +9279,8 @@
       <c r="U85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V85" s="9" t="n">
-        <v>3</v>
+      <c r="V85" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9839,13 +9839,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
@@ -10433,13 +10433,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10736,13 +10736,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -10835,13 +10835,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>4</v>
       </c>
       <c r="W101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X101" s="10" t="n">
         <v>7</v>
@@ -11318,7 +11318,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11332,17 +11332,17 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L106" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M106" s="8" t="n">
@@ -11376,11 +11376,11 @@
       <c r="U106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V106" s="9" t="n">
-        <v>1</v>
+      <c r="V106" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X106" s="9" t="n">
         <v>0</v>
@@ -11746,13 +11746,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>0</v>
@@ -13184,13 +13184,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13285,13 +13285,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>0</v>
       </c>
       <c r="V125" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
@@ -13542,7 +13542,7 @@
         <v>0</v>
       </c>
       <c r="X127" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
@@ -14976,13 +14976,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>4</v>
       </c>
       <c r="W142" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X142" s="10" t="n">
         <v>7</v>
@@ -15174,13 +15174,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15804,7 +15804,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -15822,7 +15822,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -15903,7 +15903,7 @@
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -16068,7 +16068,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -16119,7 +16119,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16251,7 +16251,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -16266,7 +16266,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">

--- a/docs/d/30/inyear.xlsx
+++ b/docs/d/30/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 16 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 47 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 47 clubs short</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="P5" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q5" s="9" t="n">
         <v>1</v>
@@ -1270,13 +1270,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1779,13 +1779,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>4</v>
       </c>
       <c r="W11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" s="10" t="n">
         <v>7</v>
@@ -2296,13 +2296,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
@@ -2607,13 +2607,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="P20" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>0</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2914,13 +2914,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>1</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="9" t="n">
         <v>0</v>
@@ -2955,8 +2955,8 @@
       <c r="T22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U22" s="9" t="n">
-        <v>0</v>
+      <c r="U22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V22" s="9" t="n">
         <v>3</v>
@@ -3324,13 +3324,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -5307,10 +5307,10 @@
         <v>20</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -5898,13 +5898,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -5942,8 +5942,8 @@
       <c r="U52" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V52" s="9" t="n">
-        <v>3</v>
+      <c r="V52" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W52" s="9" t="n">
         <v>0</v>
@@ -6591,17 +6591,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-24</v>
-      </c>
-      <c r="L59" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-4</v>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M59" s="8" t="n">
@@ -7704,13 +7704,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7809,13 +7809,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="P71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q71" s="9" t="n">
         <v>0</v>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8142,7 +8142,7 @@
         <v>1</v>
       </c>
       <c r="Q74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" s="9" t="n">
         <v>0</v>
@@ -8150,8 +8150,8 @@
       <c r="S74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T74" s="9" t="n">
-        <v>0</v>
+      <c r="T74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U74" s="9" t="n">
         <v>0</v>
@@ -8423,13 +8423,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>0</v>
       </c>
       <c r="V77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -8629,13 +8629,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -10235,13 +10235,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -10433,13 +10433,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -11233,13 +11233,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q109" s="9" t="n">
         <v>1</v>
@@ -13079,13 +13079,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>0</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
@@ -13788,13 +13788,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>0</v>
       </c>
       <c r="S139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T139" s="9" t="n">
         <v>0</v>
@@ -15075,13 +15075,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
@@ -15471,13 +15471,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>0</v>
       </c>
       <c r="V147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
@@ -15723,7 +15723,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15921,7 +15921,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15969,7 +15969,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -16053,7 +16053,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
